--- a/data/out/df_csv_condensed.xlsx
+++ b/data/out/df_csv_condensed.xlsx
@@ -732,7 +732,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1076,7 +1080,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>No</t>
@@ -1420,7 +1428,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>No</t>
@@ -1760,7 +1772,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>No</t>
@@ -1930,7 +1946,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>No</t>
@@ -2100,7 +2120,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>No</t>
@@ -2444,7 +2468,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>No</t>
@@ -3310,7 +3338,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>No</t>
@@ -3476,7 +3508,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>No</t>
@@ -3994,7 +4030,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>No</t>
@@ -4338,7 +4378,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>No</t>
@@ -4682,7 +4726,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>No</t>
@@ -5374,7 +5422,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>No</t>
@@ -5544,7 +5596,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>No</t>
@@ -5714,7 +5770,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>No</t>
@@ -5884,7 +5944,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>No</t>
@@ -6054,7 +6118,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>No</t>
@@ -6224,7 +6292,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>No</t>
@@ -6394,7 +6466,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>No</t>
@@ -6912,7 +6988,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>No</t>
@@ -7078,7 +7158,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>No</t>
@@ -7248,7 +7332,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>No</t>
@@ -7592,7 +7680,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>No</t>
@@ -7936,7 +8028,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>No</t>
@@ -8280,7 +8376,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>No</t>
@@ -8450,7 +8550,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>No</t>
@@ -8620,7 +8724,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>No</t>
@@ -8964,7 +9072,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>No</t>
@@ -9308,7 +9420,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>No</t>
@@ -9822,7 +9938,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>No</t>
@@ -10166,7 +10286,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>No</t>
@@ -10336,7 +10460,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>No</t>
@@ -10506,7 +10634,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>No</t>
@@ -10846,7 +10978,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>No</t>
@@ -11016,7 +11152,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>No</t>
@@ -11186,7 +11326,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>No</t>
@@ -11356,7 +11500,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>No</t>
@@ -11526,7 +11674,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>No</t>
@@ -11696,7 +11848,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>No</t>
@@ -11866,7 +12022,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>No</t>
@@ -12210,7 +12370,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>No</t>
@@ -13250,7 +13414,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>No</t>
@@ -13420,7 +13588,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>No</t>
@@ -13590,7 +13762,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>No</t>
@@ -13760,7 +13936,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>No</t>
@@ -13930,7 +14110,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>No</t>
@@ -14100,7 +14284,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>No</t>
@@ -14270,7 +14458,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>No</t>
@@ -14614,7 +14806,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>No</t>
@@ -14958,7 +15154,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>No</t>
@@ -15128,7 +15328,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>No</t>
@@ -15298,7 +15502,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>No</t>
@@ -15642,7 +15850,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>No</t>
@@ -15986,7 +16198,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>No</t>
@@ -16504,7 +16720,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>No</t>
@@ -16674,7 +16894,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>No</t>
@@ -16840,7 +17064,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>No</t>
@@ -17010,7 +17238,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>No</t>
@@ -17180,7 +17412,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>No</t>
@@ -17350,7 +17586,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>No</t>
@@ -17868,7 +18108,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>No</t>
@@ -18038,7 +18282,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>No</t>
@@ -19252,7 +19500,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>No</t>
@@ -19422,7 +19674,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>No</t>
@@ -19592,7 +19848,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>No</t>
@@ -19762,7 +20022,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>No</t>
@@ -19932,7 +20196,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>No</t>
@@ -20450,7 +20718,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>No</t>
@@ -20620,7 +20892,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>No</t>
@@ -20964,7 +21240,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>No</t>
@@ -21134,7 +21414,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>No</t>
@@ -21478,7 +21762,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>No</t>
@@ -21822,7 +22110,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>No</t>
@@ -21992,7 +22284,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>No</t>
@@ -22336,7 +22632,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>No</t>
@@ -22854,7 +23154,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>No</t>
@@ -23198,7 +23502,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>No</t>
@@ -23368,7 +23676,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>No</t>
@@ -23538,7 +23850,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>No</t>
@@ -23708,7 +24024,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr"/>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>No</t>
@@ -23878,7 +24198,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>No</t>
@@ -24048,7 +24372,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>No</t>
@@ -25610,7 +25938,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>No</t>
@@ -25780,7 +26112,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr"/>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>No</t>
@@ -25950,7 +26286,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr"/>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>No</t>
@@ -26294,7 +26634,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>No</t>
@@ -26638,7 +26982,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>No</t>
@@ -26808,7 +27156,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>No</t>
@@ -26978,7 +27330,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr"/>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>No</t>
@@ -27148,7 +27504,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr"/>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>No</t>
@@ -27318,7 +27678,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>No</t>
@@ -27662,7 +28026,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr"/>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>No</t>
@@ -27832,7 +28200,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr"/>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>No</t>
@@ -28350,7 +28722,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z163" t="inlineStr"/>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>No</t>
@@ -28520,7 +28896,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr"/>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>No</t>
@@ -28690,7 +29070,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr"/>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>No</t>
@@ -28860,7 +29244,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>No</t>
@@ -29030,7 +29418,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>No</t>
@@ -29200,7 +29592,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr"/>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>No</t>
@@ -29718,7 +30114,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>No</t>
@@ -29888,7 +30288,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr"/>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>No</t>
@@ -30058,7 +30462,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z173" t="inlineStr"/>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>No</t>
@@ -30228,7 +30636,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>No</t>
@@ -30398,7 +30810,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>No</t>
@@ -30568,7 +30984,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>No</t>
@@ -30738,7 +31158,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>No</t>
@@ -30908,7 +31332,11 @@
           <t>&lt;NA&gt;</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>No</t>

--- a/data/out/df_csv_condensed.xlsx
+++ b/data/out/df_csv_condensed.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>[05.06] Setting</t>
+          <t>[05.06] Location</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
